--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:43:48+00:00</t>
+    <t>2026-09-03T17:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T17:01:55+00:00</t>
+    <t>2026-09-04T05:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T05:29:06+00:00</t>
+    <t>2026-09-04T06:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4381" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5072" uniqueCount="419">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:37:14+00:00</t>
+    <t>2026-09-04T07:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -996,6 +996,145 @@
   </si>
   <si>
     <t>Datum, an dem die Familienanamnese erhoben beziehungsweise dokumentiert wurde.</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.konsanguinitaetEltern</t>
+  </si>
+  <si>
+    <t>Blutsverwandtschaft der Eltern</t>
+  </si>
+  <si>
+    <t>Gibt an, ob die biologischen Eltern des Indexpatienten blutsverwandt sind (RD-CDM v2.0.0 6.4.4).</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal</t>
+  </si>
+  <si>
+    <t>Prä- und perinatale Angaben</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.id</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.extension</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.gestationsalter</t>
+  </si>
+  <si>
+    <t>Gestationsalter bei Geburt</t>
+  </si>
+  <si>
+    <t>Vollendete Schwangerschaftswochen bei Geburt des Indexpatienten.</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.geburtsgewicht</t>
+  </si>
+  <si>
+    <t>Geburtsgewicht in g</t>
+  </si>
+  <si>
+    <t>Geburtsgewicht des Indexpatienten in Gramm.</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.geburtslaenge</t>
+  </si>
+  <si>
+    <t>Geburtslänge in cm</t>
+  </si>
+  <si>
+    <t>Körperlänge des Indexpatienten bei Geburt in Zentimetern.</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit</t>
+  </si>
+  <si>
+    <t>Funktionsfähigkeit und Behinderung (ICF)</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.id</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.extension</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.icfCode</t>
+  </si>
+  <si>
+    <t>ICF-Code</t>
+  </si>
+  <si>
+    <t>Kode der Internationalen Klassifikation der Funktionsfähigkeit, Behinderung und Gesundheit.</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.beurteilungsmerkmal</t>
+  </si>
+  <si>
+    <t>Beurteilungsmerkmal</t>
+  </si>
+  <si>
+    <t>WHO-Qualifier zum ICF-Kode. Ihre Zahl ist je Kapitel verschieden: Körperstrukturen tragen drei, Aktivitäten und Partizipation zwei.</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.erhebungsdatum</t>
+  </si>
+  <si>
+    <t>Erhebungsdatum</t>
+  </si>
+  <si>
+    <t>Datum der ICF-Einstufung.</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme</t>
+  </si>
+  <si>
+    <t>Teilnahme an Registern</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.id</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.extension</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.registerName</t>
+  </si>
+  <si>
+    <t>Register</t>
+  </si>
+  <si>
+    <t>Register, an dem der Indexpatient teilnimmt, insbesondere ein Register eines Europäischen Referenznetzwerks (ERN).</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.teilnahmestatus</t>
+  </si>
+  <si>
+    <t>Teilnahmestatus</t>
+  </si>
+  <si>
+    <t>Status der Teilnahme am Register.</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.teilnahmezeitraum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Teilnahmezeitraum</t>
+  </si>
+  <si>
+    <t>Zeitraum der Teilnahme am Register.</t>
   </si>
   <si>
     <t>Seltene.therapieForschung</t>
@@ -1452,7 +1591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ138"/>
+  <dimension ref="A1:AJ160"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
@@ -12816,7 +12955,7 @@
         <v>74</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>73</v>
@@ -12828,13 +12967,13 @@
         <v>73</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>323</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -12891,21 +13030,21 @@
         <v>74</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -12916,7 +13055,7 @@
         <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>73</v>
@@ -12928,13 +13067,13 @@
         <v>73</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>83</v>
+        <v>326</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>84</v>
+        <v>326</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -12985,38 +13124,38 @@
         <v>73</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>85</v>
+        <v>325</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -13028,17 +13167,15 @@
         <v>73</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
         <v>73</v>
@@ -13075,43 +13212,43 @@
         <v>73</v>
       </c>
       <c r="AB115" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC115" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE115" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -13124,26 +13261,24 @@
         <v>73</v>
       </c>
       <c r="I116" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J116" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K116" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O116" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>73</v>
       </c>
@@ -13179,19 +13314,19 @@
         <v>73</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -13208,14 +13343,14 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -13228,22 +13363,26 @@
         <v>73</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>328</v>
+        <v>105</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N117" s="2"/>
-      <c r="O117" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P117" t="s" s="2">
         <v>73</v>
       </c>
@@ -13291,7 +13430,7 @@
         <v>73</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>327</v>
+        <v>108</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -13303,15 +13442,15 @@
         <v>73</v>
       </c>
       <c r="AJ117" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13334,13 +13473,13 @@
         <v>73</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>82</v>
+        <v>199</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>83</v>
+        <v>331</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>84</v>
+        <v>332</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13391,7 +13530,7 @@
         <v>73</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -13408,21 +13547,21 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G119" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H119" t="s" s="2">
         <v>73</v>
@@ -13434,17 +13573,15 @@
         <v>73</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>89</v>
+        <v>334</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>335</v>
+      </c>
+      <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
         <v>73</v>
@@ -13481,75 +13618,71 @@
         <v>73</v>
       </c>
       <c r="AB119" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC119" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE119" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>95</v>
+        <v>333</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH119" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI119" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E120" s="2"/>
       <c r="F120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G120" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I120" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J120" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>105</v>
+        <v>337</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
         <v>73</v>
       </c>
@@ -13597,27 +13730,27 @@
         <v>73</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>108</v>
+        <v>336</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH120" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI120" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ120" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13628,7 +13761,7 @@
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>73</v>
@@ -13640,13 +13773,13 @@
         <v>73</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13697,27 +13830,27 @@
         <v>73</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13728,7 +13861,7 @@
         <v>74</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>73</v>
@@ -13740,13 +13873,13 @@
         <v>73</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>335</v>
+        <v>83</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>336</v>
+        <v>84</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13797,13 +13930,13 @@
         <v>73</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>334</v>
+        <v>85</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>73</v>
@@ -13814,14 +13947,14 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
@@ -13840,15 +13973,17 @@
         <v>73</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>338</v>
+        <v>89</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>73</v>
@@ -13885,19 +14020,19 @@
         <v>73</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>337</v>
+        <v>95</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
@@ -13909,47 +14044,51 @@
         <v>73</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O124" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P124" t="s" s="2">
         <v>73</v>
       </c>
@@ -13997,38 +14136,38 @@
         <v>73</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ124" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>73</v>
@@ -14040,17 +14179,15 @@
         <v>73</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>89</v>
+        <v>345</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>73</v>
@@ -14087,43 +14224,43 @@
         <v>73</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC125" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>95</v>
+        <v>344</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E126" s="2"/>
       <c r="F126" t="s" s="2">
@@ -14136,26 +14273,22 @@
         <v>73</v>
       </c>
       <c r="I126" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>105</v>
+        <v>348</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N126" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O126" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
         <v>73</v>
       </c>
@@ -14203,7 +14336,7 @@
         <v>73</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>108</v>
+        <v>347</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -14215,15 +14348,15 @@
         <v>73</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14246,13 +14379,13 @@
         <v>73</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>343</v>
+        <v>110</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14303,7 +14436,7 @@
         <v>73</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>74</v>
@@ -14320,10 +14453,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14334,7 +14467,7 @@
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>73</v>
@@ -14346,13 +14479,13 @@
         <v>73</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14403,27 +14536,27 @@
         <v>73</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14446,13 +14579,13 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>351</v>
+        <v>83</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>352</v>
+        <v>84</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14503,7 +14636,7 @@
         <v>73</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>349</v>
+        <v>85</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
@@ -14520,14 +14653,14 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
@@ -14546,15 +14679,17 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>354</v>
+        <v>89</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N130" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>73</v>
@@ -14591,19 +14726,19 @@
         <v>73</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>353</v>
+        <v>95</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -14615,47 +14750,51 @@
         <v>73</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G131" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>83</v>
+        <v>105</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O131" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>73</v>
       </c>
@@ -14703,38 +14842,38 @@
         <v>73</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH131" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ131" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>73</v>
@@ -14746,17 +14885,15 @@
         <v>73</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>89</v>
+        <v>359</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="N132" s="2"/>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
         <v>73</v>
@@ -14793,75 +14930,71 @@
         <v>73</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC132" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>95</v>
+        <v>358</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>103</v>
+        <v>73</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I133" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J133" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>105</v>
+        <v>362</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="O133" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>363</v>
+      </c>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
       <c r="P133" t="s" s="2">
         <v>73</v>
       </c>
@@ -14909,27 +15042,27 @@
         <v>73</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>108</v>
+        <v>361</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ133" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -14940,7 +15073,7 @@
         <v>74</v>
       </c>
       <c r="G134" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H134" t="s" s="2">
         <v>73</v>
@@ -14952,13 +15085,13 @@
         <v>73</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>114</v>
+        <v>365</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15009,13 +15142,13 @@
         <v>73</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>73</v>
@@ -15026,10 +15159,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15052,13 +15185,13 @@
         <v>73</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15109,7 +15242,7 @@
         <v>73</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -15121,15 +15254,15 @@
         <v>73</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15152,13 +15285,13 @@
         <v>73</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>365</v>
+        <v>83</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>366</v>
+        <v>84</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15209,7 +15342,7 @@
         <v>73</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>364</v>
+        <v>85</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -15226,21 +15359,21 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>73</v>
@@ -15252,15 +15385,17 @@
         <v>73</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>368</v>
+        <v>89</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N137" s="2"/>
+        <v>90</v>
+      </c>
+      <c r="N137" t="s" s="2">
+        <v>91</v>
+      </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>73</v>
@@ -15297,43 +15432,43 @@
         <v>73</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>367</v>
+        <v>95</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -15346,22 +15481,26 @@
         <v>73</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>371</v>
+        <v>105</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N138" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O138" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>73</v>
       </c>
@@ -15409,7 +15548,7 @@
         <v>73</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>370</v>
+        <v>108</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
@@ -15421,6 +15560,2224 @@
         <v>73</v>
       </c>
       <c r="AJ138" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B139" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="C139" s="2"/>
+      <c r="D139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E139" s="2"/>
+      <c r="F139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K139" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M139" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q139" s="2"/>
+      <c r="R139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF139" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AG139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH139" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI139" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ139" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B140" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C140" s="2"/>
+      <c r="D140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E140" s="2"/>
+      <c r="F140" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K140" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L140" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M140" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q140" s="2"/>
+      <c r="R140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF140" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG140" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH140" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI140" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ140" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="B141" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="C141" s="2"/>
+      <c r="D141" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E141" s="2"/>
+      <c r="F141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K141" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L141" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M141" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N141" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O141" s="2"/>
+      <c r="P141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q141" s="2"/>
+      <c r="R141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB141" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC141" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE141" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF141" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG141" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH141" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI141" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ141" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="B142" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="C142" s="2"/>
+      <c r="D142" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E142" s="2"/>
+      <c r="F142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I142" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J142" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K142" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L142" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M142" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N142" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O142" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q142" s="2"/>
+      <c r="R142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF142" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG142" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH142" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI142" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ142" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="B143" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="C143" s="2"/>
+      <c r="D143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E143" s="2"/>
+      <c r="F143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G143" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K143" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L143" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="M143" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+      <c r="P143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q143" s="2"/>
+      <c r="R143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF143" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AG143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH143" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI143" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ143" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="B144" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="C144" s="2"/>
+      <c r="D144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E144" s="2"/>
+      <c r="F144" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G144" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K144" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L144" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M144" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+      <c r="P144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q144" s="2"/>
+      <c r="R144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF144" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AG144" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH144" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI144" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ144" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B145" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C145" s="2"/>
+      <c r="D145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E145" s="2"/>
+      <c r="F145" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K145" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M145" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
+      <c r="P145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q145" s="2"/>
+      <c r="R145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF145" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AG145" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH145" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI145" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ145" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="B146" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="C146" s="2"/>
+      <c r="D146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E146" s="2"/>
+      <c r="F146" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K146" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L146" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M146" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N146" s="2"/>
+      <c r="O146" s="2"/>
+      <c r="P146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q146" s="2"/>
+      <c r="R146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B147" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C147" s="2"/>
+      <c r="D147" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E147" s="2"/>
+      <c r="F147" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G147" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K147" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N147" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O147" s="2"/>
+      <c r="P147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q147" s="2"/>
+      <c r="R147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB147" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC147" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE147" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF147" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG147" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH147" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI147" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ147" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="B148" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="D148" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E148" s="2"/>
+      <c r="F148" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G148" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I148" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J148" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K148" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L148" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M148" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N148" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q148" s="2"/>
+      <c r="R148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF148" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG148" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH148" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI148" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ148" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="N149" s="2"/>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="B150" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C150" s="2"/>
+      <c r="D150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E150" s="2"/>
+      <c r="F150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K150" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L150" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M150" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
+      <c r="P150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q150" s="2"/>
+      <c r="R150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF150" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI150" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ150" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B151" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="C151" s="2"/>
+      <c r="D151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E151" s="2"/>
+      <c r="F151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K151" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L151" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="M151" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="N151" s="2"/>
+      <c r="O151" s="2"/>
+      <c r="P151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q151" s="2"/>
+      <c r="R151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF151" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AG151" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH151" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI151" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ151" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B152" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="C152" s="2"/>
+      <c r="D152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E152" s="2"/>
+      <c r="F152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K152" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L152" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="M152" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N152" s="2"/>
+      <c r="O152" s="2"/>
+      <c r="P152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q152" s="2"/>
+      <c r="R152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF152" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG152" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH152" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI152" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ152" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B153" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C153" s="2"/>
+      <c r="D153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E153" s="2"/>
+      <c r="F153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K153" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="L153" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="M153" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="N153" s="2"/>
+      <c r="O153" s="2"/>
+      <c r="P153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q153" s="2"/>
+      <c r="R153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF153" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AG153" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH153" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI153" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ153" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="B154" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C154" s="2"/>
+      <c r="D154" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="E154" s="2"/>
+      <c r="F154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G154" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K154" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L154" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="M154" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="N154" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O154" s="2"/>
+      <c r="P154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q154" s="2"/>
+      <c r="R154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB154" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="AC154" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AD154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE154" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AF154" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AG154" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH154" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI154" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ154" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="B155" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="C155" s="2"/>
+      <c r="D155" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="E155" s="2"/>
+      <c r="F155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G155" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I155" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="J155" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="K155" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="L155" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M155" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="N155" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O155" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q155" s="2"/>
+      <c r="R155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF155" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AG155" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH155" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI155" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ155" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="B156" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="C156" s="2"/>
+      <c r="D156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E156" s="2"/>
+      <c r="F156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G156" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K156" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="M156" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="N156" s="2"/>
+      <c r="O156" s="2"/>
+      <c r="P156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q156" s="2"/>
+      <c r="R156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF156" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AG156" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH156" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI156" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ156" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="C157" s="2"/>
+      <c r="D157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E157" s="2"/>
+      <c r="F157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G157" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K157" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L157" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M157" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="N157" s="2"/>
+      <c r="O157" s="2"/>
+      <c r="P157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q157" s="2"/>
+      <c r="R157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF157" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI157" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ157" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="C158" s="2"/>
+      <c r="D158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E158" s="2"/>
+      <c r="F158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K158" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L158" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="M158" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="N158" s="2"/>
+      <c r="O158" s="2"/>
+      <c r="P158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q158" s="2"/>
+      <c r="R158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="B159" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C159" s="2"/>
+      <c r="D159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E159" s="2"/>
+      <c r="F159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K159" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="L159" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="M159" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="N159" s="2"/>
+      <c r="O159" s="2"/>
+      <c r="P159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q159" s="2"/>
+      <c r="R159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF159" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG159" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH159" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI159" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ159" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B160" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="C160" s="2"/>
+      <c r="D160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E160" s="2"/>
+      <c r="F160" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G160" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K160" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M160" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="N160" s="2"/>
+      <c r="O160" s="2"/>
+      <c r="P160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF160" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG160" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH160" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T07:02:52+00:00</t>
+    <t>2026-09-04T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:01:15+00:00</t>
+    <t>2026-09-04T11:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:35:42+00:00</t>
+    <t>2026-09-04T11:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:20+00:00</t>
+    <t>2026-09-04T12:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/LogicalModel/Seltene</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/LogicalModel/mii-lm-seltene</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:44:12+00:00</t>
+    <t>2026-09-04T13:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,7 +231,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>Seltene</t>
+    <t>mii-lm-seltene</t>
   </si>
   <si>
     <t/>
@@ -258,7 +258,7 @@
 </t>
   </si>
   <si>
-    <t>Seltene.id</t>
+    <t>mii-lm-seltene.id</t>
   </si>
   <si>
     <t>1</t>
@@ -277,7 +277,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>Seltene.extension</t>
+    <t>mii-lm-seltene.extension</t>
   </si>
   <si>
     <t>extensions
@@ -314,7 +314,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -324,13 +324,13 @@
     <t>Diagnose</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.id</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.extension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.modifierExtension</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -353,7 +353,7 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.untersuchungsdatum</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t xml:space="preserve">date
@@ -366,7 +366,7 @@
     <t>Datum der durchgeführten Untersuchung eines SE-Patienten.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.untersuchungsanlass</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.untersuchungsanlass</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -379,22 +379,22 @@
     <t>Grund für den Besuch des SE-Patienten.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
     <t>Phänotypisierung</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.id</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.extension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
   </si>
   <si>
     <t>HPO-Term des Symptoms</t>
@@ -403,7 +403,7 @@
     <t>Phänotypisierung des SE-Patienten mittels HPO-Term (Human Phenotype Ontology) oder anderer Terminologien (SNOMED CT, ICD-10, LOINC).</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoExcluded</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoExcluded</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -416,7 +416,7 @@
     <t>Gibt an, ob das HPO-Merkmal explizit ausgeschlossen wurde (negated finding). Abgeleitet aus valueCodeableConcept: LOINC LA9634-2 'Absent' = true, LA9633-4 'Present' = false. Folgt HL7 Phenomics IG Muster.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoStatus</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoStatus</t>
   </si>
   <si>
     <t>Status HPO-Term</t>
@@ -425,7 +425,7 @@
     <t>Status oder Schweregrad des Phänotyps (Present/Absent/Severity).</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
   </si>
   <si>
     <t>Version HPO-Term</t>
@@ -434,22 +434,22 @@
     <t>Kennzeichnung der genutzten Version des ausgewählten HPO-Terms.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom</t>
   </si>
   <si>
     <t>Zeitraum des Symptom</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.id</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.extension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.zeitraumSymptom</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.zeitraumSymptom</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -462,7 +462,7 @@
     <t>Startdatum und bei Bedarf Periode der ersten Symptome/Anzeichen.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.lebensphase</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.lebensphase</t>
   </si>
   <si>
     <t>Lebensphase Symptom</t>
@@ -471,7 +471,7 @@
     <t>Lebensphase, in der das Symptom aufgetreten ist.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.alterSymptom</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.alterSymptom</t>
   </si>
   <si>
     <t xml:space="preserve">integer
@@ -484,7 +484,7 @@
     <t>Alter beim Auftreten der ersten Symptome/Anzeichen.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.verlaufSymptom</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.verlaufSymptom</t>
   </si>
   <si>
     <t>Verlauf Symptom</t>
@@ -493,22 +493,22 @@
     <t>Änderung des Verlaufs des Symptoms seit der vorherigen Untersuchung.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose</t>
   </si>
   <si>
     <t>Zeitraum der klinischen SE-Diagnose</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.id</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.extension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.zeitpunktKlinischeDia</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.zeitpunktKlinischeDia</t>
   </si>
   <si>
     <t>Zeitpunkt klinische SE-Diagnose</t>
@@ -517,7 +517,7 @@
     <t>Auswahl der Altersangabe (Lebensphase) des Zeitpunktes der klinsichen SE-Diagnose.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.feststellungsdatumKlinischeDia</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.feststellungsdatumKlinischeDia</t>
   </si>
   <si>
     <t>Feststellungsdatum klinische SE-Diagnose</t>
@@ -526,7 +526,7 @@
     <t>Datum, an dem die klinische SE-Diagnose festgestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.alterKlinischeDia</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.alterKlinischeDia</t>
   </si>
   <si>
     <t>Alter bei klinischer SE-Diagnose</t>
@@ -535,22 +535,22 @@
     <t>Alter, in dem die klinische SE-Diagnose gestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose</t>
   </si>
   <si>
     <t>Zeitraum der genetischen SE-Diagnose</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.id</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.extension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.zeitpunktGenDia</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.zeitpunktGenDia</t>
   </si>
   <si>
     <t>Zeitpunkt genetische SE-Diagnose</t>
@@ -559,7 +559,7 @@
     <t>Auswahl der Altersangabe (Lebensphase) des Zeitpunktes der genetischen SE-Diagnose.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.feststellungsdatumGenDia</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.feststellungsdatumGenDia</t>
   </si>
   <si>
     <t>Feststellungsdatum genetische SE-Diagnose</t>
@@ -568,7 +568,7 @@
     <t>Datum, an dem die genetische SE-Diagnose festgestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.alterGenDia</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.alterGenDia</t>
   </si>
   <si>
     <t>Alter bei genetischer SE-Diagnose</t>
@@ -577,7 +577,7 @@
     <t>Alter, in dem die genetische SE-Diagnose gestellt wurde.</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.genDiaFehlendePenetranz</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.genDiaFehlendePenetranz</t>
   </si>
   <si>
     <t>Genetische Diagnose mit fehlender Penetranz</t>
@@ -586,7 +586,7 @@
     <t>Gibt an, ob bei einer genetischen Diagnose die Penetranz (Wahrscheinlichkeit Genotyp bildet Phänotyp aus) fehlt</t>
   </si>
   <si>
-    <t>Seltene.anamneseUndDiagnostik.methodeDiagnosestellung</t>
+    <t>mii-lm-seltene.anamneseUndDiagnostik.methodeDiagnosestellung</t>
   </si>
   <si>
     <t>Methode der Diagnosestellung</t>
@@ -595,37 +595,37 @@
     <t>Gibt an, welche Methode zur Diagnosestellung verwendet wurde.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung</t>
   </si>
   <si>
     <t>Körperliche Untersuchung</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergewicht</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht</t>
   </si>
   <si>
     <t>Körpergewicht</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.koerpergewicht</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.koerpergewicht</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
@@ -638,7 +638,7 @@
     <t>Körpergewicht des SE-Patienten in kg (aus MII ICU Modul).</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.datumKoerpergewicht</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.datumKoerpergewicht</t>
   </si>
   <si>
     <t>Datum Körpergewicht</t>
@@ -647,22 +647,22 @@
     <t>Datum der Körpergewichtsmessung.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergroesse</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse</t>
   </si>
   <si>
     <t>Körpergröße</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.koerpergroesse</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.koerpergroesse</t>
   </si>
   <si>
     <t>Körpergröße in cm</t>
@@ -671,7 +671,7 @@
     <t>Körpergröße des SE-Patienten in cm (aus MII ICU Modul).</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.datumKoerpergroesse</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.datumKoerpergroesse</t>
   </si>
   <si>
     <t>Datum Körpergröße</t>
@@ -680,22 +680,22 @@
     <t>Datum der Körpergrößenmessung.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.bmi</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi</t>
   </si>
   <si>
     <t>BMI</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.bmi.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.bmi.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.bmi.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.bmi.bmi</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.bmi</t>
   </si>
   <si>
     <t>BMI SE-Patient</t>
@@ -704,7 +704,7 @@
     <t>BMI des SE-Patienten.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.bmi.datumBMI</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.datumBMI</t>
   </si>
   <si>
     <t>Datum des BMI</t>
@@ -713,22 +713,22 @@
     <t>Datum, an dem der BMI (Body Mass Index) berechnet wurde.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.kopfumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang</t>
   </si>
   <si>
     <t>Kopfumfang</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.kopfumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.kopfumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.kopfumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.kopfumfang.kopfumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.kopfumfang</t>
   </si>
   <si>
     <t>Kopfumfang in cm</t>
@@ -737,7 +737,7 @@
     <t>Kopfumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.kopfumfang.datumKopfumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.datumKopfumfang</t>
   </si>
   <si>
     <t>Datum Kopfumfang</t>
@@ -746,22 +746,22 @@
     <t>Datum der Kopfumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.bauchumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang</t>
   </si>
   <si>
     <t>Bauchumfang</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.bauchumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.bauchumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.bauchumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.bauchumfang.bauchumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.bauchumfang</t>
   </si>
   <si>
     <t>Bauchumfang in cm</t>
@@ -770,7 +770,7 @@
     <t>Bauchumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.bauchumfang.datumBauchumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.datumBauchumfang</t>
   </si>
   <si>
     <t>Datum Bauchumfang</t>
@@ -779,22 +779,22 @@
     <t>Datum der Bauchumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.taillenumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang</t>
   </si>
   <si>
     <t>Taillenumfang</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.taillenumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.taillenumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.taillenumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.taillenumfang.taillenumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.taillenumfang</t>
   </si>
   <si>
     <t>Taillenumfang in cm</t>
@@ -803,7 +803,7 @@
     <t>Taillenumfang des SE-Patienten in cm. Abzugrenzen vom Bauchumfang, der auf Nabelhöhe gemessen wird.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.taillenumfang.datumTaillenumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.datumTaillenumfang</t>
   </si>
   <si>
     <t>Datum Taillenumfang</t>
@@ -812,22 +812,22 @@
     <t>Datum der Taillenumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.hueftumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang</t>
   </si>
   <si>
     <t>Hüftumfang</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.hueftumfang.id</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.hueftumfang.extension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.hueftumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.koerperlicheUntersuchung.hueftumfang.hueftumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.hueftumfang</t>
   </si>
   <si>
     <t>Hüftumfang in cm</t>
@@ -836,7 +836,7 @@
     <t>Hüftumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.hueftumfang.datumHueftumfang</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.datumHueftumfang</t>
   </si>
   <si>
     <t>Datum Hüftumfang</t>
@@ -845,7 +845,7 @@
     <t>Datum der Hüftumfangsmessung.</t>
   </si>
   <si>
-    <t>Seltene.koerperlicheUntersuchung.blutgruppe</t>
+    <t>mii-lm-seltene.koerperlicheUntersuchung.blutgruppe</t>
   </si>
   <si>
     <t>Blutgruppe</t>
@@ -854,37 +854,37 @@
     <t>Blutgruppe des SE-Patienten (AB0 und Rhesusfaktor).</t>
   </si>
   <si>
-    <t>Seltene.persoenlicheInfosIndexpatient</t>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Persönliche Informationen des Indexpatienten</t>
   </si>
   <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.id</t>
-  </si>
-  <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.extension</t>
-  </si>
-  <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod</t>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod</t>
   </si>
   <si>
     <t>Tod</t>
   </si>
   <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod.id</t>
-  </si>
-  <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod.extension</t>
-  </si>
-  <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod.sterbedatum</t>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.sterbedatum</t>
   </si>
   <si>
     <t>Sterbedatum</t>
@@ -893,7 +893,7 @@
     <t>Sterbedatum des Indexpatienten.</t>
   </si>
   <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod.anSEVerstorben</t>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.anSEVerstorben</t>
   </si>
   <si>
     <t>An der SE verstorben</t>
@@ -902,7 +902,7 @@
     <t>Angabe, ob der Indexpatient an der SE verstorben ist.</t>
   </si>
   <si>
-    <t>Seltene.persoenlicheInfosIndexpatient.tod.andereTodesursache</t>
+    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.andereTodesursache</t>
   </si>
   <si>
     <t>Todesursache</t>
@@ -911,22 +911,22 @@
     <t>Kodierung der Todesursache soweit bekannt (ICD-10-GM, ORPHAcodes).</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese</t>
+    <t>mii-lm-seltene.familienanamnese</t>
   </si>
   <si>
     <t>Familienanamnese</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.id</t>
-  </si>
-  <si>
-    <t>Seltene.familienanamnese.extension</t>
-  </si>
-  <si>
-    <t>Seltene.familienanamnese.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.familienanamnese.verwandtschaftsverhaeltnis</t>
+    <t>mii-lm-seltene.familienanamnese.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.familienanamnese.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.familienanamnese.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.familienanamnese.verwandtschaftsverhaeltnis</t>
   </si>
   <si>
     <t>Verwandtschaftsverhältnis</t>
@@ -935,7 +935,7 @@
     <t>Biologisches Verwandtschaftsverhältnis des Familienmitglieds zum Indexpatienten.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.geschlecht</t>
+    <t>mii-lm-seltene.familienanamnese.geschlecht</t>
   </si>
   <si>
     <t>Geschlecht</t>
@@ -944,7 +944,7 @@
     <t>Geschlecht des Familienmitglieds.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.gleicheSE</t>
+    <t>mii-lm-seltene.familienanamnese.gleicheSE</t>
   </si>
   <si>
     <t>Gleiche SE</t>
@@ -953,7 +953,7 @@
     <t>Gibt an, ob das Familienmitglied an der gleichen SE leidet wie der Indexpatient.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.andereSE</t>
+    <t>mii-lm-seltene.familienanamnese.andereSE</t>
   </si>
   <si>
     <t>Andere SE</t>
@@ -962,7 +962,7 @@
     <t>Gibt an, ob das Familienmitglied an einer anderen SE leidet als der Indexpatient.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.penetranz</t>
+    <t>mii-lm-seltene.familienanamnese.penetranz</t>
   </si>
   <si>
     <t>Penetranz</t>
@@ -971,7 +971,7 @@
     <t>Gibt an, ob bei fehlender klinscher Penetranz (Wahrscheinlichkeit Genotyp bildet Phänotyp aus) die genetische Diagnose vorliegt.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.familienmitgliedVerstorben</t>
+    <t>mii-lm-seltene.familienanamnese.familienmitgliedVerstorben</t>
   </si>
   <si>
     <t>Familienmitglied verstorben</t>
@@ -980,7 +980,7 @@
     <t>Gibt an, ob das Familienmitglied verstorben ist.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.todDurchSE</t>
+    <t>mii-lm-seltene.familienanamnese.todDurchSE</t>
   </si>
   <si>
     <t>Tod durch seltene Erkrankung</t>
@@ -989,7 +989,7 @@
     <t>Gibt an, ob die seltene Erkrankung zum Tod des Familienmitglieds beigetragen hat. Abzugrenzen von familienmitgliedVerstorben, das nur den Tod als solchen festhält.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.dokumentationsdatum</t>
+    <t>mii-lm-seltene.familienanamnese.dokumentationsdatum</t>
   </si>
   <si>
     <t>Dokumentationsdatum</t>
@@ -998,7 +998,7 @@
     <t>Datum, an dem die Familienanamnese erhoben beziehungsweise dokumentiert wurde.</t>
   </si>
   <si>
-    <t>Seltene.familienanamnese.konsanguinitaetEltern</t>
+    <t>mii-lm-seltene.familienanamnese.konsanguinitaetEltern</t>
   </si>
   <si>
     <t>Blutsverwandtschaft der Eltern</t>
@@ -1007,22 +1007,22 @@
     <t>Gibt an, ob die biologischen Eltern des Indexpatienten blutsverwandt sind (RD-CDM v2.0.0 6.4.4).</t>
   </si>
   <si>
-    <t>Seltene.perinatal</t>
+    <t>mii-lm-seltene.perinatal</t>
   </si>
   <si>
     <t>Prä- und perinatale Angaben</t>
   </si>
   <si>
-    <t>Seltene.perinatal.id</t>
-  </si>
-  <si>
-    <t>Seltene.perinatal.extension</t>
-  </si>
-  <si>
-    <t>Seltene.perinatal.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.perinatal.gestationsalter</t>
+    <t>mii-lm-seltene.perinatal.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.perinatal.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.perinatal.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.perinatal.gestationsalter</t>
   </si>
   <si>
     <t>Gestationsalter bei Geburt</t>
@@ -1031,7 +1031,7 @@
     <t>Vollendete Schwangerschaftswochen bei Geburt des Indexpatienten.</t>
   </si>
   <si>
-    <t>Seltene.perinatal.geburtsgewicht</t>
+    <t>mii-lm-seltene.perinatal.geburtsgewicht</t>
   </si>
   <si>
     <t>Geburtsgewicht in g</t>
@@ -1040,7 +1040,7 @@
     <t>Geburtsgewicht des Indexpatienten in Gramm.</t>
   </si>
   <si>
-    <t>Seltene.perinatal.geburtslaenge</t>
+    <t>mii-lm-seltene.perinatal.geburtslaenge</t>
   </si>
   <si>
     <t>Geburtslänge in cm</t>
@@ -1049,22 +1049,22 @@
     <t>Körperlänge des Indexpatienten bei Geburt in Zentimetern.</t>
   </si>
   <si>
-    <t>Seltene.funktionsfaehigkeit</t>
+    <t>mii-lm-seltene.funktionsfaehigkeit</t>
   </si>
   <si>
     <t>Funktionsfähigkeit und Behinderung (ICF)</t>
   </si>
   <si>
-    <t>Seltene.funktionsfaehigkeit.id</t>
-  </si>
-  <si>
-    <t>Seltene.funktionsfaehigkeit.extension</t>
-  </si>
-  <si>
-    <t>Seltene.funktionsfaehigkeit.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.funktionsfaehigkeit.icfCode</t>
+    <t>mii-lm-seltene.funktionsfaehigkeit.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.funktionsfaehigkeit.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.funktionsfaehigkeit.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.funktionsfaehigkeit.icfCode</t>
   </si>
   <si>
     <t>ICF-Code</t>
@@ -1073,7 +1073,7 @@
     <t>Kode der Internationalen Klassifikation der Funktionsfähigkeit, Behinderung und Gesundheit.</t>
   </si>
   <si>
-    <t>Seltene.funktionsfaehigkeit.beurteilungsmerkmal</t>
+    <t>mii-lm-seltene.funktionsfaehigkeit.beurteilungsmerkmal</t>
   </si>
   <si>
     <t>Beurteilungsmerkmal</t>
@@ -1082,7 +1082,7 @@
     <t>WHO-Qualifier zum ICF-Kode. Ihre Zahl ist je Kapitel verschieden: Körperstrukturen tragen drei, Aktivitäten und Partizipation zwei.</t>
   </si>
   <si>
-    <t>Seltene.funktionsfaehigkeit.erhebungsdatum</t>
+    <t>mii-lm-seltene.funktionsfaehigkeit.erhebungsdatum</t>
   </si>
   <si>
     <t>Erhebungsdatum</t>
@@ -1091,22 +1091,22 @@
     <t>Datum der ICF-Einstufung.</t>
   </si>
   <si>
-    <t>Seltene.registerteilnahme</t>
+    <t>mii-lm-seltene.registerteilnahme</t>
   </si>
   <si>
     <t>Teilnahme an Registern</t>
   </si>
   <si>
-    <t>Seltene.registerteilnahme.id</t>
-  </si>
-  <si>
-    <t>Seltene.registerteilnahme.extension</t>
-  </si>
-  <si>
-    <t>Seltene.registerteilnahme.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.registerteilnahme.registerName</t>
+    <t>mii-lm-seltene.registerteilnahme.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.registerteilnahme.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.registerteilnahme.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.registerteilnahme.registerName</t>
   </si>
   <si>
     <t>Register</t>
@@ -1115,7 +1115,7 @@
     <t>Register, an dem der Indexpatient teilnimmt, insbesondere ein Register eines Europäischen Referenznetzwerks (ERN).</t>
   </si>
   <si>
-    <t>Seltene.registerteilnahme.teilnahmestatus</t>
+    <t>mii-lm-seltene.registerteilnahme.teilnahmestatus</t>
   </si>
   <si>
     <t>Teilnahmestatus</t>
@@ -1124,7 +1124,7 @@
     <t>Status der Teilnahme am Register.</t>
   </si>
   <si>
-    <t>Seltene.registerteilnahme.teilnahmezeitraum</t>
+    <t>mii-lm-seltene.registerteilnahme.teilnahmezeitraum</t>
   </si>
   <si>
     <t xml:space="preserve">Period
@@ -1137,43 +1137,43 @@
     <t>Zeitraum der Teilnahme am Register.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung</t>
+    <t>mii-lm-seltene.therapieForschung</t>
   </si>
   <si>
     <t>Therapie und Forschung</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.id</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.extension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.offLabel</t>
+    <t>mii-lm-seltene.therapieForschung.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.offLabel</t>
   </si>
   <si>
     <t>Off-Label-Gabe</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.offLabel.id</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.offLabel.extension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.offLabel.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.offLabel.offLabelGabe</t>
+    <t>mii-lm-seltene.therapieForschung.offLabel.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.offLabel.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.offLabel.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.offLabel.offLabelGabe</t>
   </si>
   <si>
     <t>Gibt an, ob eine Off-Label-Gabe vorliegt.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.offLabel.offLabelMedikament</t>
+    <t>mii-lm-seltene.therapieForschung.offLabel.offLabelMedikament</t>
   </si>
   <si>
     <t>Off-Label-Medikament</t>
@@ -1182,22 +1182,22 @@
     <t>Gibt an, welches Medikament Off-Label gegeben wurde.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.studie</t>
+    <t>mii-lm-seltene.therapieForschung.studie</t>
   </si>
   <si>
     <t>Studie</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.studie.id</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.studie.extension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.studie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.studie.studienID</t>
+    <t>mii-lm-seltene.therapieForschung.studie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.studie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.studie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.studie.studienID</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -1210,7 +1210,7 @@
     <t>Eindeutige Identifikation der Studie, an der der SE-Patient teilgenommen hat.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.studie.studienStatus</t>
+    <t>mii-lm-seltene.therapieForschung.studie.studienStatus</t>
   </si>
   <si>
     <t>Studienstatus</t>
@@ -1219,7 +1219,7 @@
     <t>Aktueller Status der Studie, an der der SE-Patient teilgenommen hat (Abgeschlossen, Fortlaufend).</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.studie.studienzeitraum</t>
+    <t>mii-lm-seltene.therapieForschung.studie.studienzeitraum</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {organization-period}
@@ -1232,22 +1232,22 @@
     <t>Zeitraum, in dem der SE-Patient an der Studie teilgenommen hat.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.therapie</t>
+    <t>mii-lm-seltene.therapieForschung.therapie</t>
   </si>
   <si>
     <t>Therapie</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.therapie.id</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.therapie.extension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.therapie.modifierExtension</t>
-  </si>
-  <si>
-    <t>Seltene.therapieForschung.therapie.therapieempfehlung</t>
+    <t>mii-lm-seltene.therapieForschung.therapie.id</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.therapie.extension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.therapie.modifierExtension</t>
+  </si>
+  <si>
+    <t>mii-lm-seltene.therapieForschung.therapie.therapieempfehlung</t>
   </si>
   <si>
     <t>Eine Therapieempfehlung beschreibt eine spezifische Maßnahme oder Strategie. Sie kann eigenständig vorliegen oder referenziert einem Therapieplan zugeordnet werden. Art der Therapieempfehlung</t>
@@ -1256,7 +1256,7 @@
     <t>Gibt an, welche Therapieempfehlung vorliegt.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.therapie.durchgefuehrteTherapie</t>
+    <t>mii-lm-seltene.therapieForschung.therapie.durchgefuehrteTherapie</t>
   </si>
   <si>
     <t>Durchgeführte Therapie</t>
@@ -1265,7 +1265,7 @@
     <t>Tatsächlich durchgeführte Therapie des SE-Patienten (mit oder ohne Studie mit heilender Intention).</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.therapie.startdatumTherapie</t>
+    <t>mii-lm-seltene.therapieForschung.therapie.startdatumTherapie</t>
   </si>
   <si>
     <t>Startdatum Therapie</t>
@@ -1274,7 +1274,7 @@
     <t>Datum, an dem die Therapie begonnen hat.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.therapie.enddatumTherapie</t>
+    <t>mii-lm-seltene.therapieForschung.therapie.enddatumTherapie</t>
   </si>
   <si>
     <t>Enddatum Therapie</t>
@@ -1283,7 +1283,7 @@
     <t>Datum, an dem die Therapie beendet wurde.</t>
   </si>
   <si>
-    <t>Seltene.therapieForschung.therapie.grundEndeTherapie</t>
+    <t>mii-lm-seltene.therapieForschung.therapie.grundEndeTherapie</t>
   </si>
   <si>
     <t>Grund Ende Therapie</t>
@@ -1594,8 +1594,8 @@
   <dimension ref="A1:AJ160"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="72.3515625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="77.6796875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="77.6796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1625,7 +1625,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="72.3515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="77.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:01:37+00:00</t>
+    <t>2026-09-04T16:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/LogicalModel/mii-lm-seltene</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-seltene/StructureDefinition/LogicalModel/Seltene</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:11:50+00:00</t>
+    <t>2026-09-04T16:57:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,7 +231,7 @@
     <t>Constraint(s)</t>
   </si>
   <si>
-    <t>mii-lm-seltene</t>
+    <t>Seltene</t>
   </si>
   <si>
     <t/>
@@ -258,7 +258,7 @@
 </t>
   </si>
   <si>
-    <t>mii-lm-seltene.id</t>
+    <t>Seltene.id</t>
   </si>
   <si>
     <t>1</t>
@@ -277,7 +277,7 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>mii-lm-seltene.extension</t>
+    <t>Seltene.extension</t>
   </si>
   <si>
     <t>extensions
@@ -314,7 +314,7 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik</t>
+    <t>Seltene.anamneseUndDiagnostik</t>
   </si>
   <si>
     <t xml:space="preserve">BackboneElement
@@ -324,13 +324,13 @@
     <t>Diagnose</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.modifierExtension</t>
+    <t>Seltene.anamneseUndDiagnostik.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.modifierExtension</t>
   </si>
   <si>
     <t>extensions
@@ -353,7 +353,7 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.untersuchungsdatum</t>
+    <t>Seltene.anamneseUndDiagnostik.untersuchungsdatum</t>
   </si>
   <si>
     <t xml:space="preserve">date
@@ -366,7 +366,7 @@
     <t>Datum der durchgeführten Untersuchung eines SE-Patienten.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.untersuchungsanlass</t>
+    <t>Seltene.anamneseUndDiagnostik.untersuchungsanlass</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -379,22 +379,22 @@
     <t>Grund für den Besuch des SE-Patienten.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung</t>
   </si>
   <si>
     <t>Phänotypisierung</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoTerm</t>
   </si>
   <si>
     <t>HPO-Term des Symptoms</t>
@@ -403,7 +403,7 @@
     <t>Phänotypisierung des SE-Patienten mittels HPO-Term (Human Phenotype Ontology) oder anderer Terminologien (SNOMED CT, ICD-10, LOINC).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoExcluded</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoExcluded</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
@@ -416,7 +416,7 @@
     <t>Gibt an, ob das HPO-Merkmal explizit ausgeschlossen wurde (negated finding). Abgeleitet aus valueCodeableConcept: LOINC LA9634-2 'Absent' = true, LA9633-4 'Present' = false. Folgt HL7 Phenomics IG Muster.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoStatus</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoStatus</t>
   </si>
   <si>
     <t>Status HPO-Term</t>
@@ -425,7 +425,7 @@
     <t>Status oder Schweregrad des Phänotyps (Present/Absent/Severity).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.hpoVersion</t>
   </si>
   <si>
     <t>Version HPO-Term</t>
@@ -434,22 +434,22 @@
     <t>Kennzeichnung der genutzten Version des ausgewählten HPO-Terms.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom</t>
   </si>
   <si>
     <t>Zeitraum des Symptom</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.zeitraumSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.zeitraumSymptom</t>
   </si>
   <si>
     <t xml:space="preserve">dateTime
@@ -462,7 +462,7 @@
     <t>Startdatum und bei Bedarf Periode der ersten Symptome/Anzeichen.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.lebensphase</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.lebensphase</t>
   </si>
   <si>
     <t>Lebensphase Symptom</t>
@@ -471,7 +471,7 @@
     <t>Lebensphase, in der das Symptom aufgetreten ist.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.alterSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.zeitraumSymptom.alterSymptom</t>
   </si>
   <si>
     <t xml:space="preserve">integer
@@ -484,7 +484,7 @@
     <t>Alter beim Auftreten der ersten Symptome/Anzeichen.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.phaenotypisierung.verlaufSymptom</t>
+    <t>Seltene.anamneseUndDiagnostik.phaenotypisierung.verlaufSymptom</t>
   </si>
   <si>
     <t>Verlauf Symptom</t>
@@ -493,22 +493,22 @@
     <t>Änderung des Verlaufs des Symptoms seit der vorherigen Untersuchung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose</t>
   </si>
   <si>
     <t>Zeitraum der klinischen SE-Diagnose</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.zeitpunktKlinischeDia</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.zeitpunktKlinischeDia</t>
   </si>
   <si>
     <t>Zeitpunkt klinische SE-Diagnose</t>
@@ -517,7 +517,7 @@
     <t>Auswahl der Altersangabe (Lebensphase) des Zeitpunktes der klinsichen SE-Diagnose.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.feststellungsdatumKlinischeDia</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.feststellungsdatumKlinischeDia</t>
   </si>
   <si>
     <t>Feststellungsdatum klinische SE-Diagnose</t>
@@ -526,7 +526,7 @@
     <t>Datum, an dem die klinische SE-Diagnose festgestellt wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.klinischeDiagnose.alterKlinischeDia</t>
+    <t>Seltene.anamneseUndDiagnostik.klinischeDiagnose.alterKlinischeDia</t>
   </si>
   <si>
     <t>Alter bei klinischer SE-Diagnose</t>
@@ -535,22 +535,22 @@
     <t>Alter, in dem die klinische SE-Diagnose gestellt wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose</t>
   </si>
   <si>
     <t>Zeitraum der genetischen SE-Diagnose</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.zeitpunktGenDia</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.id</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.extension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.zeitpunktGenDia</t>
   </si>
   <si>
     <t>Zeitpunkt genetische SE-Diagnose</t>
@@ -559,7 +559,7 @@
     <t>Auswahl der Altersangabe (Lebensphase) des Zeitpunktes der genetischen SE-Diagnose.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.feststellungsdatumGenDia</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.feststellungsdatumGenDia</t>
   </si>
   <si>
     <t>Feststellungsdatum genetische SE-Diagnose</t>
@@ -568,7 +568,7 @@
     <t>Datum, an dem die genetische SE-Diagnose festgestellt wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genetischeDiagnose.alterGenDia</t>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.alterGenDia</t>
   </si>
   <si>
     <t>Alter bei genetischer SE-Diagnose</t>
@@ -577,7 +577,7 @@
     <t>Alter, in dem die genetische SE-Diagnose gestellt wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.genDiaFehlendePenetranz</t>
+    <t>Seltene.anamneseUndDiagnostik.genDiaFehlendePenetranz</t>
   </si>
   <si>
     <t>Genetische Diagnose mit fehlender Penetranz</t>
@@ -586,7 +586,7 @@
     <t>Gibt an, ob bei einer genetischen Diagnose die Penetranz (Wahrscheinlichkeit Genotyp bildet Phänotyp aus) fehlt</t>
   </si>
   <si>
-    <t>mii-lm-seltene.anamneseUndDiagnostik.methodeDiagnosestellung</t>
+    <t>Seltene.anamneseUndDiagnostik.methodeDiagnosestellung</t>
   </si>
   <si>
     <t>Methode der Diagnosestellung</t>
@@ -595,37 +595,37 @@
     <t>Gibt an, welche Methode zur Diagnosestellung verwendet wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung</t>
+    <t>Seltene.koerperlicheUntersuchung</t>
   </si>
   <si>
     <t>Körperliche Untersuchung</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht</t>
+    <t>Seltene.koerperlicheUntersuchung.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht</t>
   </si>
   <si>
     <t>Körpergewicht</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.koerpergewicht</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.koerpergewicht</t>
   </si>
   <si>
     <t xml:space="preserve">decimal
@@ -638,7 +638,7 @@
     <t>Körpergewicht des SE-Patienten in kg (aus MII ICU Modul).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergewicht.datumKoerpergewicht</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergewicht.datumKoerpergewicht</t>
   </si>
   <si>
     <t>Datum Körpergewicht</t>
@@ -647,22 +647,22 @@
     <t>Datum der Körpergewichtsmessung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse</t>
   </si>
   <si>
     <t>Körpergröße</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.koerpergroesse</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.koerpergroesse</t>
   </si>
   <si>
     <t>Körpergröße in cm</t>
@@ -671,7 +671,7 @@
     <t>Körpergröße des SE-Patienten in cm (aus MII ICU Modul).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.koerpergroesse.datumKoerpergroesse</t>
+    <t>Seltene.koerperlicheUntersuchung.koerpergroesse.datumKoerpergroesse</t>
   </si>
   <si>
     <t>Datum Körpergröße</t>
@@ -680,22 +680,22 @@
     <t>Datum der Körpergrößenmessung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi</t>
+    <t>Seltene.koerperlicheUntersuchung.bmi</t>
   </si>
   <si>
     <t>BMI</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.bmi</t>
+    <t>Seltene.koerperlicheUntersuchung.bmi.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bmi.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bmi.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bmi.bmi</t>
   </si>
   <si>
     <t>BMI SE-Patient</t>
@@ -704,7 +704,7 @@
     <t>BMI des SE-Patienten.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bmi.datumBMI</t>
+    <t>Seltene.koerperlicheUntersuchung.bmi.datumBMI</t>
   </si>
   <si>
     <t>Datum des BMI</t>
@@ -713,22 +713,22 @@
     <t>Datum, an dem der BMI (Body Mass Index) berechnet wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang</t>
   </si>
   <si>
     <t>Kopfumfang</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.kopfumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.kopfumfang</t>
   </si>
   <si>
     <t>Kopfumfang in cm</t>
@@ -737,7 +737,7 @@
     <t>Kopfumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.kopfumfang.datumKopfumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.kopfumfang.datumKopfumfang</t>
   </si>
   <si>
     <t>Datum Kopfumfang</t>
@@ -746,22 +746,22 @@
     <t>Datum der Kopfumfangsmessung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang</t>
   </si>
   <si>
     <t>Bauchumfang</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.bauchumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.bauchumfang</t>
   </si>
   <si>
     <t>Bauchumfang in cm</t>
@@ -770,7 +770,7 @@
     <t>Bauchumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.bauchumfang.datumBauchumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.bauchumfang.datumBauchumfang</t>
   </si>
   <si>
     <t>Datum Bauchumfang</t>
@@ -779,22 +779,22 @@
     <t>Datum der Bauchumfangsmessung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang</t>
   </si>
   <si>
     <t>Taillenumfang</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.taillenumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.taillenumfang</t>
   </si>
   <si>
     <t>Taillenumfang in cm</t>
@@ -803,7 +803,7 @@
     <t>Taillenumfang des SE-Patienten in cm. Abzugrenzen vom Bauchumfang, der auf Nabelhöhe gemessen wird.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.taillenumfang.datumTaillenumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.taillenumfang.datumTaillenumfang</t>
   </si>
   <si>
     <t>Datum Taillenumfang</t>
@@ -812,22 +812,22 @@
     <t>Datum der Taillenumfangsmessung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang</t>
   </si>
   <si>
     <t>Hüftumfang</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.hueftumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.id</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.extension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.hueftumfang</t>
   </si>
   <si>
     <t>Hüftumfang in cm</t>
@@ -836,7 +836,7 @@
     <t>Hüftumfang des SE-Patienten in cm.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.hueftumfang.datumHueftumfang</t>
+    <t>Seltene.koerperlicheUntersuchung.hueftumfang.datumHueftumfang</t>
   </si>
   <si>
     <t>Datum Hüftumfang</t>
@@ -845,7 +845,7 @@
     <t>Datum der Hüftumfangsmessung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.koerperlicheUntersuchung.blutgruppe</t>
+    <t>Seltene.koerperlicheUntersuchung.blutgruppe</t>
   </si>
   <si>
     <t>Blutgruppe</t>
@@ -854,37 +854,37 @@
     <t>Blutgruppe des SE-Patienten (AB0 und Rhesusfaktor).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient</t>
+    <t>Seltene.persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Persönliche Informationen des Indexpatienten</t>
   </si>
   <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.id</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.extension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod</t>
   </si>
   <si>
     <t>Tod</t>
   </si>
   <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.sterbedatum</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.id</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.extension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.sterbedatum</t>
   </si>
   <si>
     <t>Sterbedatum</t>
@@ -893,7 +893,7 @@
     <t>Sterbedatum des Indexpatienten.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.anSEVerstorben</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.anSEVerstorben</t>
   </si>
   <si>
     <t>An der SE verstorben</t>
@@ -902,7 +902,7 @@
     <t>Angabe, ob der Indexpatient an der SE verstorben ist.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.persoenlicheInfosIndexpatient.tod.andereTodesursache</t>
+    <t>Seltene.persoenlicheInfosIndexpatient.tod.andereTodesursache</t>
   </si>
   <si>
     <t>Todesursache</t>
@@ -911,22 +911,22 @@
     <t>Kodierung der Todesursache soweit bekannt (ICD-10-GM, ORPHAcodes).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese</t>
+    <t>Seltene.familienanamnese</t>
   </si>
   <si>
     <t>Familienanamnese</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.familienanamnese.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.familienanamnese.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.familienanamnese.verwandtschaftsverhaeltnis</t>
+    <t>Seltene.familienanamnese.id</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.extension</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.familienanamnese.verwandtschaftsverhaeltnis</t>
   </si>
   <si>
     <t>Verwandtschaftsverhältnis</t>
@@ -935,7 +935,7 @@
     <t>Biologisches Verwandtschaftsverhältnis des Familienmitglieds zum Indexpatienten.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.geschlecht</t>
+    <t>Seltene.familienanamnese.geschlecht</t>
   </si>
   <si>
     <t>Geschlecht</t>
@@ -944,7 +944,7 @@
     <t>Geschlecht des Familienmitglieds.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.gleicheSE</t>
+    <t>Seltene.familienanamnese.gleicheSE</t>
   </si>
   <si>
     <t>Gleiche SE</t>
@@ -953,7 +953,7 @@
     <t>Gibt an, ob das Familienmitglied an der gleichen SE leidet wie der Indexpatient.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.andereSE</t>
+    <t>Seltene.familienanamnese.andereSE</t>
   </si>
   <si>
     <t>Andere SE</t>
@@ -962,7 +962,7 @@
     <t>Gibt an, ob das Familienmitglied an einer anderen SE leidet als der Indexpatient.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.penetranz</t>
+    <t>Seltene.familienanamnese.penetranz</t>
   </si>
   <si>
     <t>Penetranz</t>
@@ -971,7 +971,7 @@
     <t>Gibt an, ob bei fehlender klinscher Penetranz (Wahrscheinlichkeit Genotyp bildet Phänotyp aus) die genetische Diagnose vorliegt.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.familienmitgliedVerstorben</t>
+    <t>Seltene.familienanamnese.familienmitgliedVerstorben</t>
   </si>
   <si>
     <t>Familienmitglied verstorben</t>
@@ -980,7 +980,7 @@
     <t>Gibt an, ob das Familienmitglied verstorben ist.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.todDurchSE</t>
+    <t>Seltene.familienanamnese.todDurchSE</t>
   </si>
   <si>
     <t>Tod durch seltene Erkrankung</t>
@@ -989,7 +989,7 @@
     <t>Gibt an, ob die seltene Erkrankung zum Tod des Familienmitglieds beigetragen hat. Abzugrenzen von familienmitgliedVerstorben, das nur den Tod als solchen festhält.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.dokumentationsdatum</t>
+    <t>Seltene.familienanamnese.dokumentationsdatum</t>
   </si>
   <si>
     <t>Dokumentationsdatum</t>
@@ -998,7 +998,7 @@
     <t>Datum, an dem die Familienanamnese erhoben beziehungsweise dokumentiert wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.familienanamnese.konsanguinitaetEltern</t>
+    <t>Seltene.familienanamnese.konsanguinitaetEltern</t>
   </si>
   <si>
     <t>Blutsverwandtschaft der Eltern</t>
@@ -1007,22 +1007,22 @@
     <t>Gibt an, ob die biologischen Eltern des Indexpatienten blutsverwandt sind (RD-CDM v2.0.0 6.4.4).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.perinatal</t>
+    <t>Seltene.perinatal</t>
   </si>
   <si>
     <t>Prä- und perinatale Angaben</t>
   </si>
   <si>
-    <t>mii-lm-seltene.perinatal.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.perinatal.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.perinatal.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.perinatal.gestationsalter</t>
+    <t>Seltene.perinatal.id</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.extension</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.perinatal.gestationsalter</t>
   </si>
   <si>
     <t>Gestationsalter bei Geburt</t>
@@ -1031,7 +1031,7 @@
     <t>Vollendete Schwangerschaftswochen bei Geburt des Indexpatienten.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.perinatal.geburtsgewicht</t>
+    <t>Seltene.perinatal.geburtsgewicht</t>
   </si>
   <si>
     <t>Geburtsgewicht in g</t>
@@ -1040,7 +1040,7 @@
     <t>Geburtsgewicht des Indexpatienten in Gramm.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.perinatal.geburtslaenge</t>
+    <t>Seltene.perinatal.geburtslaenge</t>
   </si>
   <si>
     <t>Geburtslänge in cm</t>
@@ -1049,22 +1049,22 @@
     <t>Körperlänge des Indexpatienten bei Geburt in Zentimetern.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit</t>
+    <t>Seltene.funktionsfaehigkeit</t>
   </si>
   <si>
     <t>Funktionsfähigkeit und Behinderung (ICF)</t>
   </si>
   <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit.icfCode</t>
+    <t>Seltene.funktionsfaehigkeit.id</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.extension</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.funktionsfaehigkeit.icfCode</t>
   </si>
   <si>
     <t>ICF-Code</t>
@@ -1073,7 +1073,7 @@
     <t>Kode der Internationalen Klassifikation der Funktionsfähigkeit, Behinderung und Gesundheit.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit.beurteilungsmerkmal</t>
+    <t>Seltene.funktionsfaehigkeit.beurteilungsmerkmal</t>
   </si>
   <si>
     <t>Beurteilungsmerkmal</t>
@@ -1082,7 +1082,7 @@
     <t>WHO-Qualifier zum ICF-Kode. Ihre Zahl ist je Kapitel verschieden: Körperstrukturen tragen drei, Aktivitäten und Partizipation zwei.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.funktionsfaehigkeit.erhebungsdatum</t>
+    <t>Seltene.funktionsfaehigkeit.erhebungsdatum</t>
   </si>
   <si>
     <t>Erhebungsdatum</t>
@@ -1091,22 +1091,22 @@
     <t>Datum der ICF-Einstufung.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.registerteilnahme</t>
+    <t>Seltene.registerteilnahme</t>
   </si>
   <si>
     <t>Teilnahme an Registern</t>
   </si>
   <si>
-    <t>mii-lm-seltene.registerteilnahme.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.registerteilnahme.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.registerteilnahme.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.registerteilnahme.registerName</t>
+    <t>Seltene.registerteilnahme.id</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.extension</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.registerteilnahme.registerName</t>
   </si>
   <si>
     <t>Register</t>
@@ -1115,7 +1115,7 @@
     <t>Register, an dem der Indexpatient teilnimmt, insbesondere ein Register eines Europäischen Referenznetzwerks (ERN).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.registerteilnahme.teilnahmestatus</t>
+    <t>Seltene.registerteilnahme.teilnahmestatus</t>
   </si>
   <si>
     <t>Teilnahmestatus</t>
@@ -1124,7 +1124,7 @@
     <t>Status der Teilnahme am Register.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.registerteilnahme.teilnahmezeitraum</t>
+    <t>Seltene.registerteilnahme.teilnahmezeitraum</t>
   </si>
   <si>
     <t xml:space="preserve">Period
@@ -1137,43 +1137,43 @@
     <t>Zeitraum der Teilnahme am Register.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung</t>
+    <t>Seltene.therapieForschung</t>
   </si>
   <si>
     <t>Therapie und Forschung</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.offLabel</t>
+    <t>Seltene.therapieForschung.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel</t>
   </si>
   <si>
     <t>Off-Label-Gabe</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.offLabel.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.offLabel.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.offLabel.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.offLabel.offLabelGabe</t>
+    <t>Seltene.therapieForschung.offLabel.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.offLabel.offLabelGabe</t>
   </si>
   <si>
     <t>Gibt an, ob eine Off-Label-Gabe vorliegt.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.offLabel.offLabelMedikament</t>
+    <t>Seltene.therapieForschung.offLabel.offLabelMedikament</t>
   </si>
   <si>
     <t>Off-Label-Medikament</t>
@@ -1182,22 +1182,22 @@
     <t>Gibt an, welches Medikament Off-Label gegeben wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.studie</t>
+    <t>Seltene.therapieForschung.studie</t>
   </si>
   <si>
     <t>Studie</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.studie.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.studie.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.studie.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.studie.studienID</t>
+    <t>Seltene.therapieForschung.studie.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.studie.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.studie.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.studie.studienID</t>
   </si>
   <si>
     <t xml:space="preserve">Identifier
@@ -1210,7 +1210,7 @@
     <t>Eindeutige Identifikation der Studie, an der der SE-Patient teilgenommen hat.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.studie.studienStatus</t>
+    <t>Seltene.therapieForschung.studie.studienStatus</t>
   </si>
   <si>
     <t>Studienstatus</t>
@@ -1219,7 +1219,7 @@
     <t>Aktueller Status der Studie, an der der SE-Patient teilgenommen hat (Abgeschlossen, Fortlaufend).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.studie.studienzeitraum</t>
+    <t>Seltene.therapieForschung.studie.studienzeitraum</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {organization-period}
@@ -1232,22 +1232,22 @@
     <t>Zeitraum, in dem der SE-Patient an der Studie teilgenommen hat.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.therapie</t>
+    <t>Seltene.therapieForschung.therapie</t>
   </si>
   <si>
     <t>Therapie</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.id</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.extension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.modifierExtension</t>
-  </si>
-  <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.therapieempfehlung</t>
+    <t>Seltene.therapieForschung.therapie.id</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.therapie.extension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.therapie.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.therapieForschung.therapie.therapieempfehlung</t>
   </si>
   <si>
     <t>Eine Therapieempfehlung beschreibt eine spezifische Maßnahme oder Strategie. Sie kann eigenständig vorliegen oder referenziert einem Therapieplan zugeordnet werden. Art der Therapieempfehlung</t>
@@ -1256,7 +1256,7 @@
     <t>Gibt an, welche Therapieempfehlung vorliegt.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.durchgefuehrteTherapie</t>
+    <t>Seltene.therapieForschung.therapie.durchgefuehrteTherapie</t>
   </si>
   <si>
     <t>Durchgeführte Therapie</t>
@@ -1265,7 +1265,7 @@
     <t>Tatsächlich durchgeführte Therapie des SE-Patienten (mit oder ohne Studie mit heilender Intention).</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.startdatumTherapie</t>
+    <t>Seltene.therapieForschung.therapie.startdatumTherapie</t>
   </si>
   <si>
     <t>Startdatum Therapie</t>
@@ -1274,7 +1274,7 @@
     <t>Datum, an dem die Therapie begonnen hat.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.enddatumTherapie</t>
+    <t>Seltene.therapieForschung.therapie.enddatumTherapie</t>
   </si>
   <si>
     <t>Enddatum Therapie</t>
@@ -1283,7 +1283,7 @@
     <t>Datum, an dem die Therapie beendet wurde.</t>
   </si>
   <si>
-    <t>mii-lm-seltene.therapieForschung.therapie.grundEndeTherapie</t>
+    <t>Seltene.therapieForschung.therapie.grundEndeTherapie</t>
   </si>
   <si>
     <t>Grund Ende Therapie</t>
@@ -1594,8 +1594,8 @@
   <dimension ref="A1:AJ160"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="77.6796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="77.6796875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="72.3515625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="18.19140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1625,7 +1625,7 @@
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="77.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="72.3515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:57:12+00:00</t>
+    <t>2026-09-07T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:50:41+00:00</t>
+    <t>2026-09-07T16:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:06:13+00:00</t>
+    <t>2026-09-08T09:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:37+00:00</t>
+    <t>2026-09-08T09:32:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:32:56+00:00</t>
+    <t>2026-09-08T15:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:03:47+00:00</t>
+    <t>2026-09-09T09:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:29:55+00:00</t>
+    <t>2026-09-09T10:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:02:49+00:00</t>
+    <t>2026-09-09T11:08:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:08:17+00:00</t>
+    <t>2026-09-09T11:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5072" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5103" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:49:20+00:00</t>
+    <t>2026-09-11T10:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -548,6 +548,15 @@
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.modifierExtension</t>
+  </si>
+  <si>
+    <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.omimCode</t>
+  </si>
+  <si>
+    <t>OMIM-Code</t>
+  </si>
+  <si>
+    <t>Kennung der Erkrankung in Online Mendelian Inheritance in Man. Ergaenzt die Kodierung aus dem Modul Diagnose um die genspezifische Zuordnung; fuer monogene Erkrankungen praeziser als ICD-10-GM.</t>
   </si>
   <si>
     <t>Seltene.anamneseUndDiagnostik.genetischeDiagnose.zeitpunktGenDia</t>
@@ -1591,7 +1600,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ160"/>
+  <dimension ref="A1:AJ161"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="72.3515625" customWidth="true" bestFit="true"/>
@@ -5389,7 +5398,7 @@
         <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>73</v>
@@ -5464,7 +5473,7 @@
         <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>73</v>
@@ -5501,7 +5510,7 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>177</v>
@@ -5601,7 +5610,7 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>148</v>
+        <v>110</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>180</v>
@@ -5689,7 +5698,7 @@
         <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>73</v>
@@ -5701,7 +5710,7 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>183</v>
@@ -5764,7 +5773,7 @@
         <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>73</v>
@@ -5901,13 +5910,13 @@
         <v>73</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>189</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5970,15 +5979,15 @@
         <v>73</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5989,7 +5998,7 @@
         <v>74</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>73</v>
@@ -6001,13 +6010,13 @@
         <v>73</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>83</v>
+        <v>192</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6058,38 +6067,38 @@
         <v>73</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>85</v>
+        <v>191</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
@@ -6101,17 +6110,15 @@
         <v>73</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>73</v>
@@ -6148,43 +6155,43 @@
         <v>73</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6197,26 +6204,24 @@
         <v>73</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N46" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>73</v>
       </c>
@@ -6252,19 +6257,19 @@
         <v>73</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -6281,14 +6286,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6301,22 +6306,26 @@
         <v>73</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>73</v>
       </c>
@@ -6364,7 +6373,7 @@
         <v>73</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>74</v>
@@ -6376,15 +6385,15 @@
         <v>73</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6395,7 +6404,7 @@
         <v>74</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>
@@ -6407,13 +6416,13 @@
         <v>73</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>83</v>
+        <v>197</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6464,38 +6473,38 @@
         <v>73</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>73</v>
@@ -6507,17 +6516,15 @@
         <v>73</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>73</v>
@@ -6554,43 +6561,43 @@
         <v>73</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -6603,26 +6610,24 @@
         <v>73</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K50" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O50" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>73</v>
       </c>
@@ -6658,19 +6663,19 @@
         <v>73</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -6687,42 +6692,46 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>200</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>73</v>
       </c>
@@ -6770,27 +6779,27 @@
         <v>73</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>198</v>
+        <v>108</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6813,7 +6822,7 @@
         <v>73</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>203</v>
@@ -6870,7 +6879,7 @@
         <v>73</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -6901,7 +6910,7 @@
         <v>74</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>73</v>
@@ -6913,13 +6922,13 @@
         <v>73</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>206</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6976,21 +6985,21 @@
         <v>74</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7001,7 +7010,7 @@
         <v>74</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>73</v>
@@ -7013,13 +7022,13 @@
         <v>73</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>83</v>
+        <v>209</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>84</v>
+        <v>209</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7070,38 +7079,38 @@
         <v>73</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>73</v>
@@ -7113,17 +7122,15 @@
         <v>73</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>73</v>
@@ -7160,43 +7167,43 @@
         <v>73</v>
       </c>
       <c r="AB55" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC55" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -7209,26 +7216,24 @@
         <v>73</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K56" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O56" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>73</v>
       </c>
@@ -7264,19 +7269,19 @@
         <v>73</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -7293,42 +7298,46 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>211</v>
+        <v>105</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>73</v>
       </c>
@@ -7376,19 +7385,19 @@
         <v>73</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="58">
@@ -7419,7 +7428,7 @@
         <v>73</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L58" t="s" s="2">
         <v>214</v>
@@ -7507,7 +7516,7 @@
         <v>74</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>73</v>
@@ -7519,13 +7528,13 @@
         <v>73</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
         <v>217</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7582,21 +7591,21 @@
         <v>74</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7607,7 +7616,7 @@
         <v>74</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>73</v>
@@ -7619,13 +7628,13 @@
         <v>73</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>84</v>
+        <v>220</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7676,38 +7685,38 @@
         <v>73</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>85</v>
+        <v>219</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>73</v>
@@ -7719,17 +7728,15 @@
         <v>73</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>73</v>
@@ -7766,43 +7773,43 @@
         <v>73</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -7815,26 +7822,24 @@
         <v>73</v>
       </c>
       <c r="I62" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K62" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O62" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>73</v>
       </c>
@@ -7870,19 +7875,19 @@
         <v>73</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -7899,42 +7904,46 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>222</v>
+        <v>105</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>73</v>
       </c>
@@ -7982,19 +7991,19 @@
         <v>73</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>221</v>
+        <v>108</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="64">
@@ -8025,7 +8034,7 @@
         <v>73</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>225</v>
@@ -8113,7 +8122,7 @@
         <v>74</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>73</v>
@@ -8125,13 +8134,13 @@
         <v>73</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L65" t="s" s="2">
         <v>228</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8188,21 +8197,21 @@
         <v>74</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8213,7 +8222,7 @@
         <v>74</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>73</v>
@@ -8225,13 +8234,13 @@
         <v>73</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>83</v>
+        <v>231</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>84</v>
+        <v>231</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8282,38 +8291,38 @@
         <v>73</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>73</v>
@@ -8325,17 +8334,15 @@
         <v>73</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>73</v>
@@ -8372,43 +8379,43 @@
         <v>73</v>
       </c>
       <c r="AB67" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -8421,26 +8428,24 @@
         <v>73</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K68" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N68" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O68" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>73</v>
       </c>
@@ -8476,19 +8481,19 @@
         <v>73</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>74</v>
@@ -8505,42 +8510,46 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>233</v>
+        <v>105</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>73</v>
       </c>
@@ -8588,19 +8597,19 @@
         <v>73</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>232</v>
+        <v>108</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="70">
@@ -8631,7 +8640,7 @@
         <v>73</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>236</v>
@@ -8719,7 +8728,7 @@
         <v>74</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>73</v>
@@ -8731,13 +8740,13 @@
         <v>73</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s" s="2">
         <v>239</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8794,21 +8803,21 @@
         <v>74</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8819,7 +8828,7 @@
         <v>74</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>73</v>
@@ -8831,13 +8840,13 @@
         <v>73</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>83</v>
+        <v>242</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>84</v>
+        <v>242</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8888,38 +8897,38 @@
         <v>73</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>85</v>
+        <v>241</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>73</v>
@@ -8931,17 +8940,15 @@
         <v>73</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>73</v>
@@ -8978,43 +8985,43 @@
         <v>73</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9027,26 +9034,24 @@
         <v>73</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K74" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N74" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O74" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>73</v>
       </c>
@@ -9082,19 +9087,19 @@
         <v>73</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -9111,42 +9116,46 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I75" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>244</v>
+        <v>105</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>73</v>
       </c>
@@ -9194,19 +9203,19 @@
         <v>73</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>243</v>
+        <v>108</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76">
@@ -9237,7 +9246,7 @@
         <v>73</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L76" t="s" s="2">
         <v>247</v>
@@ -9325,7 +9334,7 @@
         <v>74</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>73</v>
@@ -9337,13 +9346,13 @@
         <v>73</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
         <v>250</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9400,21 +9409,21 @@
         <v>74</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9425,7 +9434,7 @@
         <v>74</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>73</v>
@@ -9437,13 +9446,13 @@
         <v>73</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>84</v>
+        <v>253</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9494,38 +9503,38 @@
         <v>73</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>85</v>
+        <v>252</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>73</v>
@@ -9537,17 +9546,15 @@
         <v>73</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>73</v>
@@ -9584,43 +9591,43 @@
         <v>73</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -9633,26 +9640,24 @@
         <v>73</v>
       </c>
       <c r="I80" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N80" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O80" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>73</v>
       </c>
@@ -9688,19 +9693,19 @@
         <v>73</v>
       </c>
       <c r="AB80" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC80" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD80" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE80" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>74</v>
@@ -9717,42 +9722,46 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>255</v>
+        <v>105</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>73</v>
       </c>
@@ -9800,19 +9809,19 @@
         <v>73</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>254</v>
+        <v>108</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82">
@@ -9843,7 +9852,7 @@
         <v>73</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L82" t="s" s="2">
         <v>258</v>
@@ -9931,7 +9940,7 @@
         <v>74</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>73</v>
@@ -9943,13 +9952,13 @@
         <v>73</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>98</v>
+        <v>141</v>
       </c>
       <c r="L83" t="s" s="2">
         <v>261</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10006,21 +10015,21 @@
         <v>74</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10031,7 +10040,7 @@
         <v>74</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>73</v>
@@ -10043,13 +10052,13 @@
         <v>73</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>83</v>
+        <v>264</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>84</v>
+        <v>264</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10100,38 +10109,38 @@
         <v>73</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>85</v>
+        <v>263</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>73</v>
@@ -10143,17 +10152,15 @@
         <v>73</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>73</v>
@@ -10190,43 +10197,43 @@
         <v>73</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -10239,26 +10246,24 @@
         <v>73</v>
       </c>
       <c r="I86" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O86" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>73</v>
       </c>
@@ -10294,19 +10299,19 @@
         <v>73</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -10323,42 +10328,46 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>266</v>
+        <v>105</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>73</v>
       </c>
@@ -10406,19 +10415,19 @@
         <v>73</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>265</v>
+        <v>108</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="88">
@@ -10449,7 +10458,7 @@
         <v>73</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>141</v>
+        <v>202</v>
       </c>
       <c r="L88" t="s" s="2">
         <v>269</v>
@@ -10549,7 +10558,7 @@
         <v>73</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>272</v>
@@ -10637,7 +10646,7 @@
         <v>74</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>73</v>
@@ -10649,13 +10658,13 @@
         <v>73</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L90" t="s" s="2">
         <v>275</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -10712,21 +10721,21 @@
         <v>74</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10737,7 +10746,7 @@
         <v>74</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>73</v>
@@ -10749,13 +10758,13 @@
         <v>73</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>83</v>
+        <v>278</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>84</v>
+        <v>278</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10806,38 +10815,38 @@
         <v>73</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>85</v>
+        <v>277</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>73</v>
@@ -10849,17 +10858,15 @@
         <v>73</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
         <v>73</v>
@@ -10896,43 +10903,43 @@
         <v>73</v>
       </c>
       <c r="AB92" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC92" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD92" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE92" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -10945,26 +10952,24 @@
         <v>73</v>
       </c>
       <c r="I93" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K93" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O93" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>73</v>
       </c>
@@ -11000,19 +11005,19 @@
         <v>73</v>
       </c>
       <c r="AB93" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>74</v>
@@ -11029,42 +11034,46 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>280</v>
+        <v>105</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>73</v>
       </c>
@@ -11112,27 +11121,27 @@
         <v>73</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11155,13 +11164,13 @@
         <v>73</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>83</v>
+        <v>283</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>84</v>
+        <v>283</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11212,7 +11221,7 @@
         <v>73</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -11224,26 +11233,26 @@
         <v>73</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>73</v>
@@ -11255,17 +11264,15 @@
         <v>73</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N96" s="2"/>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>73</v>
@@ -11302,43 +11309,43 @@
         <v>73</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -11351,26 +11358,24 @@
         <v>73</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N97" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O97" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>73</v>
       </c>
@@ -11406,19 +11411,19 @@
         <v>73</v>
       </c>
       <c r="AB97" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -11435,42 +11440,46 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I98" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>285</v>
+        <v>105</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>73</v>
       </c>
@@ -11518,19 +11527,19 @@
         <v>73</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="99">
@@ -11561,7 +11570,7 @@
         <v>73</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L99" t="s" s="2">
         <v>288</v>
@@ -11649,7 +11658,7 @@
         <v>74</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>73</v>
@@ -11724,7 +11733,7 @@
         <v>74</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI100" t="s" s="2">
         <v>73</v>
@@ -11761,13 +11770,13 @@
         <v>73</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>294</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -11830,15 +11839,15 @@
         <v>73</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11849,7 +11858,7 @@
         <v>74</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>73</v>
@@ -11861,13 +11870,13 @@
         <v>73</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -11918,38 +11927,38 @@
         <v>73</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>85</v>
+        <v>296</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>73</v>
@@ -11961,17 +11970,15 @@
         <v>73</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>73</v>
@@ -12008,43 +12015,43 @@
         <v>73</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC103" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD103" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -12057,26 +12064,24 @@
         <v>73</v>
       </c>
       <c r="I104" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K104" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N104" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O104" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
         <v>73</v>
       </c>
@@ -12112,19 +12117,19 @@
         <v>73</v>
       </c>
       <c r="AB104" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC104" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD104" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE104" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>74</v>
@@ -12141,42 +12146,46 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I105" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>299</v>
+        <v>105</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>73</v>
       </c>
@@ -12224,19 +12233,19 @@
         <v>73</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>298</v>
+        <v>108</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="106">
@@ -12355,7 +12364,7 @@
         <v>74</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>73</v>
@@ -12430,7 +12439,7 @@
         <v>74</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>73</v>
@@ -12555,7 +12564,7 @@
         <v>74</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>73</v>
@@ -12630,7 +12639,7 @@
         <v>74</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>73</v>
@@ -12867,7 +12876,7 @@
         <v>73</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
         <v>320</v>
@@ -12967,7 +12976,7 @@
         <v>73</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L113" t="s" s="2">
         <v>323</v>
@@ -13055,7 +13064,7 @@
         <v>74</v>
       </c>
       <c r="G114" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H114" t="s" s="2">
         <v>73</v>
@@ -13067,13 +13076,13 @@
         <v>73</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L114" t="s" s="2">
         <v>326</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13130,21 +13139,21 @@
         <v>74</v>
       </c>
       <c r="AH114" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI114" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ114" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13155,7 +13164,7 @@
         <v>74</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>73</v>
@@ -13167,13 +13176,13 @@
         <v>73</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>84</v>
+        <v>329</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13224,38 +13233,38 @@
         <v>73</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>85</v>
+        <v>328</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ115" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>73</v>
@@ -13267,17 +13276,15 @@
         <v>73</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>73</v>
@@ -13314,43 +13321,43 @@
         <v>73</v>
       </c>
       <c r="AB116" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC116" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD116" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE116" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ116" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -13363,26 +13370,24 @@
         <v>73</v>
       </c>
       <c r="I117" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J117" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K117" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O117" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>73</v>
       </c>
@@ -13418,19 +13423,19 @@
         <v>73</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE117" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -13447,42 +13452,46 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I118" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J118" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>199</v>
+        <v>88</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>331</v>
+        <v>105</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P118" t="s" s="2">
         <v>73</v>
       </c>
@@ -13530,19 +13539,19 @@
         <v>73</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>330</v>
+        <v>108</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="119">
@@ -13573,7 +13582,7 @@
         <v>73</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L119" t="s" s="2">
         <v>334</v>
@@ -13673,7 +13682,7 @@
         <v>73</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L120" t="s" s="2">
         <v>337</v>
@@ -13761,7 +13770,7 @@
         <v>74</v>
       </c>
       <c r="G121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H121" t="s" s="2">
         <v>73</v>
@@ -13773,13 +13782,13 @@
         <v>73</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="L121" t="s" s="2">
         <v>340</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -13836,21 +13845,21 @@
         <v>74</v>
       </c>
       <c r="AH121" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI121" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13861,7 +13870,7 @@
         <v>74</v>
       </c>
       <c r="G122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H122" t="s" s="2">
         <v>73</v>
@@ -13873,13 +13882,13 @@
         <v>73</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>83</v>
+        <v>343</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -13930,38 +13939,38 @@
         <v>73</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>85</v>
+        <v>342</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH122" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI122" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>73</v>
@@ -13973,17 +13982,15 @@
         <v>73</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N123" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>73</v>
@@ -14020,43 +14027,43 @@
         <v>73</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -14069,26 +14076,24 @@
         <v>73</v>
       </c>
       <c r="I124" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J124" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K124" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N124" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O124" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>73</v>
       </c>
@@ -14124,19 +14129,19 @@
         <v>73</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC124" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD124" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -14153,42 +14158,46 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>345</v>
+        <v>105</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>73</v>
       </c>
@@ -14236,19 +14245,19 @@
         <v>73</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>344</v>
+        <v>108</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="126">
@@ -14267,7 +14276,7 @@
         <v>74</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>73</v>
@@ -14342,7 +14351,7 @@
         <v>74</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>73</v>
@@ -14367,7 +14376,7 @@
         <v>74</v>
       </c>
       <c r="G127" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H127" t="s" s="2">
         <v>73</v>
@@ -14379,7 +14388,7 @@
         <v>73</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L127" t="s" s="2">
         <v>351</v>
@@ -14442,7 +14451,7 @@
         <v>74</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>73</v>
@@ -14467,7 +14476,7 @@
         <v>74</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>73</v>
@@ -14479,13 +14488,13 @@
         <v>73</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="L128" t="s" s="2">
         <v>354</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14542,21 +14551,21 @@
         <v>74</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -14567,7 +14576,7 @@
         <v>74</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>73</v>
@@ -14579,13 +14588,13 @@
         <v>73</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>83</v>
+        <v>357</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>84</v>
+        <v>357</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -14636,38 +14645,38 @@
         <v>73</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>85</v>
+        <v>356</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G130" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H130" t="s" s="2">
         <v>73</v>
@@ -14679,17 +14688,15 @@
         <v>73</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N130" s="2"/>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>73</v>
@@ -14726,43 +14733,43 @@
         <v>73</v>
       </c>
       <c r="AB130" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC130" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD130" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE130" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH130" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI130" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ130" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -14775,26 +14782,24 @@
         <v>73</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J131" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K131" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O131" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>73</v>
       </c>
@@ -14830,19 +14835,19 @@
         <v>73</v>
       </c>
       <c r="AB131" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC131" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD131" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE131" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -14859,42 +14864,46 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I132" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J132" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>359</v>
+        <v>105</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N132" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O132" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P132" t="s" s="2">
         <v>73</v>
       </c>
@@ -14942,19 +14951,19 @@
         <v>73</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>358</v>
+        <v>108</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ132" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="133">
@@ -15085,13 +15094,13 @@
         <v>73</v>
       </c>
       <c r="K134" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L134" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="L134" t="s" s="2">
+      <c r="M134" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M134" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15159,10 +15168,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15173,7 +15182,7 @@
         <v>74</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>73</v>
@@ -15185,13 +15194,13 @@
         <v>73</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>98</v>
+        <v>368</v>
       </c>
       <c r="L135" t="s" s="2">
         <v>369</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15242,27 +15251,27 @@
         <v>73</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH135" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI135" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ135" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15273,7 +15282,7 @@
         <v>74</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>73</v>
@@ -15285,13 +15294,13 @@
         <v>73</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>83</v>
+        <v>372</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15342,38 +15351,38 @@
         <v>73</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>85</v>
+        <v>371</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ136" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E137" s="2"/>
       <c r="F137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>73</v>
@@ -15385,17 +15394,15 @@
         <v>73</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N137" s="2"/>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
         <v>73</v>
@@ -15432,43 +15439,43 @@
         <v>73</v>
       </c>
       <c r="AB137" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC137" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE137" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ137" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
@@ -15481,26 +15488,24 @@
         <v>73</v>
       </c>
       <c r="I138" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J138" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K138" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N138" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O138" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>73</v>
       </c>
@@ -15536,19 +15541,19 @@
         <v>73</v>
       </c>
       <c r="AB138" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC138" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD138" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE138" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>74</v>
@@ -15565,14 +15570,14 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E139" s="2"/>
       <c r="F139" t="s" s="2">
@@ -15585,22 +15590,26 @@
         <v>73</v>
       </c>
       <c r="I139" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J139" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>374</v>
+        <v>105</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N139" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O139" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>73</v>
       </c>
@@ -15648,7 +15657,7 @@
         <v>73</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>373</v>
+        <v>108</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>74</v>
@@ -15660,15 +15669,15 @@
         <v>73</v>
       </c>
       <c r="AJ139" t="s" s="2">
-        <v>79</v>
+        <v>96</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15679,7 +15688,7 @@
         <v>74</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>73</v>
@@ -15691,13 +15700,13 @@
         <v>73</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>83</v>
+        <v>377</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -15748,38 +15757,38 @@
         <v>73</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>85</v>
+        <v>376</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ140" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E141" s="2"/>
       <c r="F141" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G141" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H141" t="s" s="2">
         <v>73</v>
@@ -15791,17 +15800,15 @@
         <v>73</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N141" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N141" s="2"/>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
         <v>73</v>
@@ -15838,43 +15845,43 @@
         <v>73</v>
       </c>
       <c r="AB141" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC141" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD141" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE141" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH141" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI141" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ141" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E142" s="2"/>
       <c r="F142" t="s" s="2">
@@ -15887,26 +15894,24 @@
         <v>73</v>
       </c>
       <c r="I142" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J142" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K142" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N142" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O142" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
         <v>73</v>
       </c>
@@ -15942,19 +15947,19 @@
         <v>73</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC142" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD142" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE142" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
@@ -15971,42 +15976,46 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I143" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J143" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>374</v>
+        <v>105</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O143" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P143" t="s" s="2">
         <v>73</v>
       </c>
@@ -16054,27 +16063,27 @@
         <v>73</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>378</v>
+        <v>108</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16085,7 +16094,7 @@
         <v>74</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
         <v>73</v>
@@ -16100,7 +16109,7 @@
         <v>114</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="M144" t="s" s="2">
         <v>382</v>
@@ -16154,13 +16163,13 @@
         <v>73</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI144" t="s" s="2">
         <v>73</v>
@@ -16197,13 +16206,13 @@
         <v>73</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="L145" t="s" s="2">
         <v>384</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -16266,15 +16275,15 @@
         <v>73</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16285,7 +16294,7 @@
         <v>74</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>73</v>
@@ -16297,13 +16306,13 @@
         <v>73</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>83</v>
+        <v>387</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -16354,38 +16363,38 @@
         <v>73</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>85</v>
+        <v>386</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ146" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>73</v>
@@ -16397,17 +16406,15 @@
         <v>73</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>73</v>
@@ -16444,43 +16451,43 @@
         <v>73</v>
       </c>
       <c r="AB147" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC147" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD147" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE147" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
@@ -16493,26 +16500,24 @@
         <v>73</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J148" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K148" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N148" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O148" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>73</v>
       </c>
@@ -16548,19 +16553,19 @@
         <v>73</v>
       </c>
       <c r="AB148" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC148" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD148" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE148" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
@@ -16577,42 +16582,46 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E149" s="2"/>
       <c r="F149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G149" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H149" t="s" s="2">
         <v>73</v>
       </c>
       <c r="I149" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J149" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>389</v>
+        <v>88</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>390</v>
+        <v>105</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N149" s="2"/>
-      <c r="O149" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O149" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P149" t="s" s="2">
         <v>73</v>
       </c>
@@ -16660,27 +16669,27 @@
         <v>73</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>388</v>
+        <v>108</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH149" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI149" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ149" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -16703,7 +16712,7 @@
         <v>73</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>114</v>
+        <v>392</v>
       </c>
       <c r="L150" t="s" s="2">
         <v>393</v>
@@ -16760,7 +16769,7 @@
         <v>73</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
@@ -16803,13 +16812,13 @@
         <v>73</v>
       </c>
       <c r="K151" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L151" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="L151" t="s" s="2">
+      <c r="M151" t="s" s="2">
         <v>397</v>
-      </c>
-      <c r="M151" t="s" s="2">
-        <v>398</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -16877,10 +16886,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -16891,7 +16900,7 @@
         <v>74</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>73</v>
@@ -16903,13 +16912,13 @@
         <v>73</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>98</v>
+        <v>399</v>
       </c>
       <c r="L152" t="s" s="2">
         <v>400</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -16960,27 +16969,27 @@
         <v>73</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH152" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI152" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ152" t="s" s="2">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -16991,7 +17000,7 @@
         <v>74</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>73</v>
@@ -17003,13 +17012,13 @@
         <v>73</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>84</v>
+        <v>403</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17060,38 +17069,38 @@
         <v>73</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>85</v>
+        <v>402</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>73</v>
@@ -17103,17 +17112,15 @@
         <v>73</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="N154" t="s" s="2">
-        <v>91</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
         <v>73</v>
@@ -17150,43 +17157,43 @@
         <v>73</v>
       </c>
       <c r="AB154" t="s" s="2">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="AC154" t="s" s="2">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="AD154" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE154" t="s" s="2">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ154" t="s" s="2">
-        <v>96</v>
+        <v>73</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
@@ -17199,26 +17206,24 @@
         <v>73</v>
       </c>
       <c r="I155" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="J155" t="s" s="2">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K155" t="s" s="2">
         <v>88</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="N155" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="O155" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
         <v>73</v>
       </c>
@@ -17254,19 +17259,19 @@
         <v>73</v>
       </c>
       <c r="AB155" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="AC155" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AD155" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE155" t="s" s="2">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>74</v>
@@ -17283,14 +17288,14 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -17303,22 +17308,26 @@
         <v>73</v>
       </c>
       <c r="I156" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="J156" t="s" s="2">
-        <v>73</v>
+        <v>104</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>405</v>
+        <v>105</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="N156" s="2"/>
-      <c r="O156" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N156" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="O156" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="P156" t="s" s="2">
         <v>73</v>
       </c>
@@ -17366,7 +17375,7 @@
         <v>73</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>404</v>
+        <v>108</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>74</v>
@@ -17378,7 +17387,7 @@
         <v>73</v>
       </c>
       <c r="AJ156" t="s" s="2">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157">
@@ -17497,7 +17506,7 @@
         <v>74</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H158" t="s" s="2">
         <v>73</v>
@@ -17509,7 +17518,7 @@
         <v>73</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="L158" t="s" s="2">
         <v>411</v>
@@ -17572,7 +17581,7 @@
         <v>74</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>73</v>
@@ -17697,7 +17706,7 @@
         <v>74</v>
       </c>
       <c r="G160" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H160" t="s" s="2">
         <v>73</v>
@@ -17709,7 +17718,7 @@
         <v>73</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="L160" t="s" s="2">
         <v>417</v>
@@ -17772,12 +17781,112 @@
         <v>74</v>
       </c>
       <c r="AH160" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI160" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ160" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B161" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="C161" s="2"/>
+      <c r="D161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E161" s="2"/>
+      <c r="F161" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G161" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="AI160" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ160" t="s" s="2">
+      <c r="H161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K161" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L161" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M161" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="N161" s="2"/>
+      <c r="O161" s="2"/>
+      <c r="P161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q161" s="2"/>
+      <c r="R161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF161" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG161" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH161" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI161" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ161" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:52:45+00:00</t>
+    <t>2026-09-11T12:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
+++ b/branches/dev/StructureDefinition-mii-lm-seltene.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5103" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5104" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -54,10 +54,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:45:52+00:00</t>
+    <t>2026-09-11T14:10:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -112,9 +115,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1491,79 +1491,81 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
         <v>3</v>
@@ -1571,18 +1573,18 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>33</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1784,7 +1786,7 @@
         <v>9</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
